--- a/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="156">
   <si>
     <t>Property</t>
   </si>
@@ -428,6 +428,22 @@
   </si>
   <si>
     <t>Procedure.bodySite</t>
+  </si>
+  <si>
+    <t>Prozedur.DetaillierteAnatomischeStruktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>Detaillierte anatomische Struktur</t>
+  </si>
+  <si>
+    <t>Detaillierte Angaben zu der patientenbezogenen anatomischen Struktur oder Lokalisation, auf die sich die Prozedur bezieht. Das Element kann verwendet werden, wenn die kodierte Angabe der Körperstelle allein nicht die für den Anwendungsfall erforderliche Genauigkeit bietet.</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension('http://hl7.org/fhir/StructureDefinition/bodySite').valueReference</t>
   </si>
   <si>
     <t>Prozedur.Durchfuehrungsabsicht</t>
@@ -785,7 +801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.5546875" customWidth="true" bestFit="true"/>
@@ -798,7 +814,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="21.45703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2514,7 +2530,7 @@
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>
@@ -2526,13 +2542,13 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2589,7 +2605,7 @@
         <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>75</v>
@@ -2598,15 +2614,15 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2614,7 +2630,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>84</v>
@@ -2629,7 +2645,7 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>140</v>
@@ -2686,10 +2702,10 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>84</v>
@@ -2717,7 +2733,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>84</v>
@@ -2732,13 +2748,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2792,7 +2808,7 @@
         <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>84</v>
@@ -2804,15 +2820,15 @@
         <v>75</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2835,13 +2851,13 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2892,7 +2908,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -2907,7 +2923,110 @@
         <v>75</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-dev</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-prozedur.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
